--- a/TestSuites/FileServer/docs/RequirementSpecifications/MS-SMB2_ServerRequirementSpecification_v80.xlsx
+++ b/TestSuites/FileServer/docs/RequirementSpecifications/MS-SMB2_ServerRequirementSpecification_v80.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PxC\WindowsProtocolTestSuites\TestSuites\FileServer\docs\RequirementSpecifications\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lmakutano\source\repos\WindowsProtocolTestSuites\TestSuites\FileServer\docs\RequirementSpecifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DC6C63D-31DD-4798-864B-ADF960FBDB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2976E34C-C789-45D9-929C-E219F1F65923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="297">
   <si>
     <t>Req ID</t>
   </si>
@@ -1193,6 +1193,9 @@
   </si>
   <si>
     <t>Test Implemented : FileInfo_Query_FilePositionInformation. Diff is in reference number</t>
+  </si>
+  <si>
+    <t>Implementated</t>
   </si>
 </sst>
 </file>
@@ -1744,15 +1747,28 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1762,19 +1778,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1855,6 +1858,21 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <strike/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.59996337778862885"/>
@@ -1862,36 +1880,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.59996337778862885"/>
@@ -1899,6 +1887,21 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <strike/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.59996337778862885"/>
@@ -1906,21 +1909,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.59996337778862885"/>
@@ -1928,16 +1916,31 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <strike/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2626,14 +2629,6 @@
   </Schema>
   <Map ID="12" Name="ReqTable_Map" RootElement="ReqTable" SchemaID="Schema4" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
-</file>
-
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3051,152 +3046,152 @@
       <c r="L4" s="23"/>
     </row>
     <row r="5" spans="2:12" ht="21">
-      <c r="B5" s="103" t="s">
+      <c r="B5" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
       <c r="L5" s="23"/>
     </row>
     <row r="6" spans="2:12">
       <c r="B6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="107" t="s">
+      <c r="C6" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="113"/>
+      <c r="K6" s="113"/>
       <c r="L6" s="23"/>
     </row>
     <row r="7" spans="2:12">
       <c r="B7" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="106" t="s">
+      <c r="C7" s="111" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
+      <c r="D7" s="111"/>
+      <c r="E7" s="111"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="111"/>
       <c r="L7" s="23"/>
     </row>
     <row r="8" spans="2:12">
       <c r="B8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="106" t="s">
+      <c r="C8" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="106"/>
-      <c r="E8" s="106"/>
-      <c r="F8" s="106"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="106"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="106"/>
-      <c r="K8" s="106"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="111"/>
       <c r="L8" s="23"/>
     </row>
     <row r="9" spans="2:12">
       <c r="B9" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="106" t="s">
+      <c r="C9" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="106"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="106"/>
-      <c r="K9" s="106"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+      <c r="F9" s="111"/>
+      <c r="G9" s="111"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="111"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="111"/>
       <c r="L9" s="23"/>
     </row>
     <row r="10" spans="2:12" ht="78.75" customHeight="1">
       <c r="B10" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="104" t="s">
+      <c r="C10" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="105"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
       <c r="L10" s="23"/>
     </row>
     <row r="11" spans="2:12">
       <c r="B11" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="104" t="s">
+      <c r="C11" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="105"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="108"/>
       <c r="L11" s="23"/>
     </row>
     <row r="12" spans="2:12" ht="33.75" customHeight="1">
       <c r="B12" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="104" t="s">
+      <c r="C12" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="105"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="108"/>
+      <c r="K12" s="108"/>
       <c r="L12" s="23"/>
     </row>
     <row r="13" spans="2:12">
       <c r="B13" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="109" t="s">
+      <c r="C13" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="109"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="109"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="109"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="103"/>
+      <c r="K13" s="103"/>
       <c r="L13" s="23"/>
     </row>
     <row r="14" spans="2:12">
@@ -3209,13 +3204,13 @@
       <c r="D14" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="110"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
       <c r="L14" s="23"/>
     </row>
     <row r="15" spans="2:12" ht="15" customHeight="1">
@@ -3228,13 +3223,13 @@
       <c r="D15" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="111"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="105"/>
       <c r="L15" s="23"/>
     </row>
     <row r="16" spans="2:12" ht="30">
@@ -3247,13 +3242,13 @@
       <c r="D16" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="105"/>
+      <c r="K16" s="105"/>
       <c r="L16" s="23"/>
     </row>
     <row r="17" spans="1:13" ht="45">
@@ -3266,40 +3261,40 @@
       <c r="D17" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="112"/>
-      <c r="F17" s="112"/>
-      <c r="G17" s="112"/>
-      <c r="H17" s="112"/>
-      <c r="I17" s="112"/>
-      <c r="J17" s="112"/>
-      <c r="K17" s="112"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
       <c r="L17" s="23"/>
     </row>
     <row r="18" spans="1:13" ht="30" customHeight="1">
       <c r="B18" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="109" t="s">
+      <c r="C18" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="109"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="109"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="103"/>
       <c r="L18" s="23"/>
     </row>
     <row r="19" spans="1:13" ht="85.5" customHeight="1">
       <c r="B19" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="109" t="s">
+      <c r="C19" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="113"/>
+      <c r="D19" s="109"/>
       <c r="E19" s="44"/>
       <c r="F19" s="44"/>
       <c r="G19" s="48"/>
@@ -3313,17 +3308,17 @@
       <c r="B20" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="109" t="s">
+      <c r="C20" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="109"/>
-      <c r="E20" s="109"/>
-      <c r="F20" s="109"/>
-      <c r="G20" s="109"/>
-      <c r="H20" s="109"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="103"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="103"/>
     </row>
     <row r="21" spans="1:13" ht="30">
       <c r="A21" s="1" t="s">
@@ -3496,7 +3491,7 @@
         <v>285</v>
       </c>
       <c r="L25" s="90" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="M25" s="17" t="s">
         <v>68</v>
@@ -4291,7 +4286,7 @@
         <v>285</v>
       </c>
       <c r="L49" s="90" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="M49" s="14" t="s">
         <v>125</v>
@@ -4326,7 +4321,7 @@
         <v>285</v>
       </c>
       <c r="L50" s="90" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="M50" s="14" t="s">
         <v>125</v>
@@ -5636,6 +5631,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="C9:K9"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C6:K6"/>
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="E14:K17"/>
     <mergeCell ref="C18:K18"/>
@@ -5643,48 +5644,42 @@
     <mergeCell ref="C10:K10"/>
     <mergeCell ref="C12:K12"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="C11:K11"/>
-    <mergeCell ref="C9:K9"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="C6:K6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B65:K65 C66:K67 B89:L89">
-    <cfRule type="expression" dxfId="52" priority="2832">
+    <cfRule type="expression" dxfId="52" priority="2833">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="2832">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="2833">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="50" priority="2834">
       <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D68 H68:K68 F68:F88 H69 J69:K69 H70:K70 H71:H80 J71:K80 H81:K86 H87:H88 J87:K88">
-    <cfRule type="expression" dxfId="49" priority="139">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
+    <cfRule type="expression" dxfId="49" priority="142">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"Section Deleted")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="140">
+    <cfRule type="expression" dxfId="48" priority="141">
+      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="47" priority="140">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="141">
-      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="142">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"Section Deleted")</formula>
+    <cfRule type="expression" dxfId="46" priority="139">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E90">
-    <cfRule type="expression" dxfId="45" priority="2366">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
+    <cfRule type="expression" dxfId="45" priority="2368">
+      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="44" priority="2367">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="2368">
-      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
+    <cfRule type="expression" dxfId="43" priority="2366">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
@@ -5713,139 +5708,135 @@
     <cfRule type="expression" dxfId="36" priority="48">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="49">
+    <cfRule type="expression" dxfId="35" priority="50">
+      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="49">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="50">
-      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22:I29">
-    <cfRule type="expression" dxfId="33" priority="45">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
+    <cfRule type="expression" dxfId="33" priority="47">
+      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="32" priority="46">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="47">
-      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
+    <cfRule type="expression" dxfId="31" priority="45">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I67 I89">
+  <conditionalFormatting sqref="I22:I67">
     <cfRule type="expression" dxfId="30" priority="2527">
       <formula>(VLOOKUP(I22,$B$15:$D$18,2,FALSE)="In")</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="29" priority="2526">
+      <formula>NOT(VLOOKUP(I22,$B$15:$D$18,2,FALSE)="In")</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I68 I70 I81:I86">
-    <cfRule type="expression" dxfId="29" priority="67">
+    <cfRule type="expression" dxfId="28" priority="67">
       <formula>NOT(VLOOKUP(I68,$B$13:$D$16,2,FALSE)="In")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="68">
+    <cfRule type="expression" dxfId="27" priority="68">
       <formula>(VLOOKUP(I68,$B$13:$D$16,2,FALSE)="In")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I69">
-    <cfRule type="expression" dxfId="27" priority="11">
-      <formula>NOT(VLOOKUP(I69,$B$15:$D$18,2,FALSE)="In")</formula>
+    <cfRule type="expression" dxfId="26" priority="13">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="12">
-      <formula>(VLOOKUP(I69,$B$15:$D$18,2,FALSE)="In")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="13">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
+    <cfRule type="expression" dxfId="25" priority="15">
+      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="14">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="15">
+    <cfRule type="expression" dxfId="23" priority="12">
+      <formula>(VLOOKUP(I69,$B$15:$D$18,2,FALSE)="In")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="11">
+      <formula>NOT(VLOOKUP(I69,$B$15:$D$18,2,FALSE)="In")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I71:I80">
+    <cfRule type="expression" dxfId="21" priority="10">
+      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="9">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="8">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="7">
+      <formula>(VLOOKUP(I71,$B$15:$D$18,2,FALSE)="In")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="6">
+      <formula>NOT(VLOOKUP(I71,$B$15:$D$18,2,FALSE)="In")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I87:I88">
+    <cfRule type="expression" dxfId="16" priority="3">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="4">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="5">
       <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I71:I80">
-    <cfRule type="expression" dxfId="22" priority="6">
-      <formula>NOT(VLOOKUP(I71,$B$15:$D$18,2,FALSE)="In")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="7">
-      <formula>(VLOOKUP(I71,$B$15:$D$18,2,FALSE)="In")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="8">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="9">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="10">
-      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I87:I88">
-    <cfRule type="expression" dxfId="17" priority="3">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="5">
-      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I87:I88">
-    <cfRule type="expression" dxfId="14" priority="1">
-      <formula>NOT(VLOOKUP(I87,$B$15:$D$18,2,FALSE)="In")</formula>
-    </cfRule>
+  <conditionalFormatting sqref="I87:I89">
     <cfRule type="expression" dxfId="13" priority="2">
       <formula>(VLOOKUP(I87,$B$15:$D$18,2,FALSE)="In")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I67 I89">
-    <cfRule type="expression" dxfId="12" priority="2526">
-      <formula>NOT(VLOOKUP(I22,$B$15:$D$18,2,FALSE)="In")</formula>
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>NOT(VLOOKUP(I87,$B$15:$D$18,2,FALSE)="In")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J22:J29">
     <cfRule type="expression" dxfId="11" priority="40">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="41">
+    <cfRule type="expression" dxfId="10" priority="42">
+      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="41">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="42">
-      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:K33 B22:C65 K35 C66:C67 B66:B88">
-    <cfRule type="expression" dxfId="8" priority="34">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
+    <cfRule type="expression" dxfId="8" priority="36">
+      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="35">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="36">
-      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
+    <cfRule type="expression" dxfId="6" priority="34">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L30 D30:J35 L32 L34:L35 D36:L51 D52:E52 G52:L52 D53:L62 D63:E64 G63:L64">
-    <cfRule type="expression" dxfId="5" priority="2828">
+    <cfRule type="expression" dxfId="5" priority="2749">
+      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2828">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2829">
+    <cfRule type="expression" dxfId="3" priority="2829">
       <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L30 D30:J35 L32 L34:L35 D36:L51 D52:E52 G52:L52 D53:L62 D63:E64 G63:L64">
-    <cfRule type="expression" dxfId="3" priority="2749">
-      <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L65:L67">
     <cfRule type="expression" dxfId="2" priority="1481">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"SectionDeleted")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="1482">
+    <cfRule type="expression" dxfId="1" priority="1483">
+      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="1482">
       <formula>EXACT(INDIRECT("P"&amp;ROW()),"Deleted")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1483">
-      <formula>EXACT(INDIRECT("L"&amp;ROW()),"Deleted")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="8">
@@ -5885,6 +5876,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="7c105c98-15e8-4194-801a-83691ae15f2a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c105c98-15e8-4194-801a-83691ae15f2a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BED2F3CDE748FA41BF5F42361F25EE98" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c06012bcc83371980fa6877e0d8abe9a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7c105c98-15e8-4194-801a-83691ae15f2a" xmlns:ns3="6ac11e62-b72a-435e-930f-506a7299734f" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7a0cd2d2b6ce19ae2c80eae5833a1a3d" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6167,46 +6181,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="7c105c98-15e8-4194-801a-83691ae15f2a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c105c98-15e8-4194-801a-83691ae15f2a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D22529B-1952-44C5-8439-4FCE8BC8969E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6D33261-F3C6-4621-88F1-D76E5ABE1865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7c105c98-15e8-4194-801a-83691ae15f2a"/>
-    <ds:schemaRef ds:uri="6ac11e62-b72a-435e-930f-506a7299734f"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6231,9 +6209,22 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6D33261-F3C6-4621-88F1-D76E5ABE1865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D22529B-1952-44C5-8439-4FCE8BC8969E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="7c105c98-15e8-4194-801a-83691ae15f2a"/>
+    <ds:schemaRef ds:uri="6ac11e62-b72a-435e-930f-506a7299734f"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
